--- a/cypress/fixtures/refBancaria.xlsx
+++ b/cypress/fixtures/refBancaria.xlsx
@@ -76,7 +76,7 @@
     <t>Local</t>
   </si>
   <si>
-    <t>25145010000021</t>
+    <t>25145010000023</t>
   </si>
   <si>
     <t>Monetarios</t>
@@ -136,13 +136,13 @@
     <t>Correo Personal</t>
   </si>
   <si>
-    <t>alberto694@gmail.com</t>
+    <t>alberto696@gmail.com</t>
   </si>
   <si>
     <t>Celular</t>
   </si>
   <si>
-    <t>11119082540</t>
+    <t>11119082546</t>
   </si>
   <si>
     <t>Juan</t>
